--- a/data/trans_bre/P1401-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1401-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -634,22 +634,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,71</t>
+          <t>-0,49; 4,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,19</t>
+          <t>0,43; 4,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,47</t>
+          <t>-1,17; 1,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-42,45; 1239,79</t>
+          <t>-51,94; 873,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,6; 518,42</t>
+          <t>-69,73; 411,87</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-23,27%</t>
+          <t>-24,08%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,86</t>
+          <t>-0,77; 1,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,23</t>
+          <t>-0,99; 1,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,03</t>
+          <t>-2,18; 0,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,4; 521,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 461,15</t>
+          <t>-82,37; 774,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,16; 106,95</t>
+          <t>-69,83; 89,32</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,8</t>
+          <t>-2,73; 2,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,6</t>
+          <t>-0,25; 5,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,32</t>
+          <t>-1,0; 2,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 268,39</t>
+          <t>-83,59; 339,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 667,79</t>
+          <t>-29,42; 614,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 219,32</t>
+          <t>-40,32; 217,99</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,25</t>
+          <t>0,35; 4,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,64</t>
+          <t>-0,72; 3,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,11</t>
+          <t>-0,87; 2,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 1348,06</t>
+          <t>-7,22; 1773,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,07; 568,48</t>
+          <t>-45,48; 526,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 218,22</t>
+          <t>-31,98; 271,44</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 2,05</t>
+          <t>-4,89; 2,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,47</t>
+          <t>-3,09; 0,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,43</t>
+          <t>-0,99; 3,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 312,37</t>
+          <t>-34,55; 279,4</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,7%</t>
+          <t>-23,64%</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,45</t>
+          <t>-2,37; 1,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,61</t>
+          <t>-0,6; 1,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,33</t>
+          <t>-2,66; 1,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 76,14</t>
+          <t>-66,83; 66,77</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-53,37%</t>
+          <t>-38,09%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,04</t>
+          <t>0,73; 3,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,15</t>
+          <t>0,29; 2,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; -0,17</t>
+          <t>-2,33; 0,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,16; 1118,16</t>
+          <t>39,78; 1046,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1045,32</t>
+          <t>2,24; 936,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-81,38; -8,21</t>
+          <t>-67,04; 21,31</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>103,7%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,72</t>
+          <t>-0,41; 1,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,82</t>
+          <t>0,27; 2,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,37</t>
+          <t>-0,42; 2,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,3; 364,28</t>
+          <t>-37,65; 376,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 898,31</t>
+          <t>5,62; 904,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,72; 432,06</t>
+          <t>-16,78; 147,36</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,56</t>
+          <t>0,31; 1,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,81</t>
+          <t>0,51; 1,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,79</t>
+          <t>-0,44; 0,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,58; 170,25</t>
+          <t>19,84; 166,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>46,74; 254,37</t>
+          <t>47,99; 249,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 48,63</t>
+          <t>-18,13; 41,71</t>
         </is>
       </c>
     </row>
